--- a/src/OpenXmlHtml.Tests/SpreadsheetIntegrationTests.SingleLinkHyperlink.DotNet.verified.xlsx
+++ b/src/OpenXmlHtml.Tests/SpreadsheetIntegrationTests.SingleLinkHyperlink.DotNet.verified.xlsx
@@ -34,7 +34,7 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="DeterministicId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="DeterministicId1" display="full report"/>
   </hyperlinks>
 </worksheet>
 </file>